--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,36 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pistol_range</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>900</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>knife_range</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>64</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -2,27 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20430" yWindow="5445" windowWidth="17970" windowHeight="15435" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -50,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -505,7 +511,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -520,11 +526,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cook_player_speed</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>260</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>요리(밤) 스테이지 플레이어 이동 속도(px/s)</t>
         </is>
       </c>
     </row>

--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -1,40 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68dca1814c1352fc/Documents/hilling-game/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_57A6907C54408CCF696A18B6431F5EBFA54DA14E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E25205-2FCA-49A6-B6DA-04383870E927}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20430" yWindow="5445" windowWidth="17970" windowHeight="15435" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="19395" yWindow="5040" windowWidth="17970" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="balance" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>player_speed</t>
+  </si>
+  <si>
+    <t>탐험 플레이어 이동 속도(px/s)</t>
+  </si>
+  <si>
+    <t>scavenge_seconds</t>
+  </si>
+  <si>
+    <t>탐험 제한 시간(초)</t>
+  </si>
+  <si>
+    <t>night_seconds</t>
+  </si>
+  <si>
+    <t>밤 쿠킹 세션 시간(초)</t>
+  </si>
+  <si>
+    <t>target_satisfaction</t>
+  </si>
+  <si>
+    <t>밤 성공에 필요한 만족 목표치</t>
+  </si>
+  <si>
+    <t>pistol_range</t>
+  </si>
+  <si>
+    <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
+  </si>
+  <si>
+    <t>knife_range</t>
+  </si>
+  <si>
+    <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
+  </si>
+  <si>
+    <t>cook_player_speed</t>
+  </si>
+  <si>
+    <t>요리(밤) 스테이지 플레이어 이동 속도(px/s)</t>
+  </si>
+  <si>
+    <t>camp_god_x</t>
+  </si>
+  <si>
+    <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
+  </si>
+  <si>
+    <t>camp_god_y</t>
+  </si>
+  <si>
+    <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
+  </si>
+  <si>
+    <t>camp_player_x</t>
+  </si>
+  <si>
+    <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
+  </si>
+  <si>
+    <t>camp_player_y</t>
+  </si>
+  <si>
+    <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -53,81 +138,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,142 +444,149 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>player_speed</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>280</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>탐험 플레이어 이동 속도(px/s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>scavenge_seconds</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>150</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>탐험 제한 시간(초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>night_seconds</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
         <v>60</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>밤 쿠킹 세션 시간(초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>target_satisfaction</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
         <v>60</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>밤 성공에 필요한 만족 목표치</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>pistol_range</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
         <v>160</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>knife_range</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
         <v>60</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cook_player_speed</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>260</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>요리(밤) 스테이지 플레이어 이동 속도(px/s)</t>
-        </is>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>280</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>0.44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>0.45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -1,125 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68dca1814c1352fc/Documents/hilling-game/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_57A6907C54408CCF696A18B6431F5EBFA54DA14E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E25205-2FCA-49A6-B6DA-04383870E927}"/>
   <bookViews>
-    <workbookView xWindow="19395" yWindow="5040" windowWidth="17970" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19395" yWindow="5040" windowWidth="17970" windowHeight="15435" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>player_speed</t>
-  </si>
-  <si>
-    <t>탐험 플레이어 이동 속도(px/s)</t>
-  </si>
-  <si>
-    <t>scavenge_seconds</t>
-  </si>
-  <si>
-    <t>탐험 제한 시간(초)</t>
-  </si>
-  <si>
-    <t>night_seconds</t>
-  </si>
-  <si>
-    <t>밤 쿠킹 세션 시간(초)</t>
-  </si>
-  <si>
-    <t>target_satisfaction</t>
-  </si>
-  <si>
-    <t>밤 성공에 필요한 만족 목표치</t>
-  </si>
-  <si>
-    <t>pistol_range</t>
-  </si>
-  <si>
-    <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
-  </si>
-  <si>
-    <t>knife_range</t>
-  </si>
-  <si>
-    <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
-  </si>
-  <si>
-    <t>cook_player_speed</t>
-  </si>
-  <si>
-    <t>요리(밤) 스테이지 플레이어 이동 속도(px/s)</t>
-  </si>
-  <si>
-    <t>camp_god_x</t>
-  </si>
-  <si>
-    <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
-  </si>
-  <si>
-    <t>camp_god_y</t>
-  </si>
-  <si>
-    <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
-  </si>
-  <si>
-    <t>camp_player_x</t>
-  </si>
-  <si>
-    <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
-  </si>
-  <si>
-    <t>camp_player_y</t>
-  </si>
-  <si>
-    <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -138,26 +53,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,149 +414,322 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>player_speed</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>280</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>탐험 플레이어 이동 속도(px/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>scavenge_seconds</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>탐험 제한 시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>night_seconds</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>밤 쿠킹 세션 시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>target_satisfaction</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>밤 성공에 필요한 만족 목표치</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pistol_range</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>160</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>knife_range</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cook_player_speed</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>280</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>요리(밤) 스테이지 플레이어 이동 속도(px/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>camp_god_x</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>camp_god_y</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>camp_player_x</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>camp_player_y</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>stat_hp_base</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>플레이어 기본 체력</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>stat_hp_per_level</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>체력 강화 레벨당 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>stat_hp_max_level</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>150</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>160</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>체력 최대 강화 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>stat_hp_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>15</v>
       </c>
-      <c r="B8">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>체력 강화 기본 비용(실제=base*(레벨+1))</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stat_speed_base</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>280</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>0.8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>0.44</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>플레이어 기본 이동속도(px/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stat_speed_per_level</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11">
-        <v>0.45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12">
-        <v>0.5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>이동속도 강화 레벨당 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stat_speed_max_level</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>이동속도 최대 강화 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stat_speed_cost</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>이동속도 강화 기본 비용(실제=base*(레벨+1))</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -537,193 +537,178 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cook_player_speed</t>
+          <t>camp_god_x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>요리(밤) 스테이지 플레이어 이동 속도(px/s)</t>
+          <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>camp_god_x</t>
+          <t>camp_god_y</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
+          <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>camp_god_y</t>
+          <t>camp_player_x</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
+          <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>camp_player_x</t>
+          <t>camp_player_y</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
+          <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>camp_player_y</t>
+          <t>stat_hp_base</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
+          <t>플레이어 기본 체력</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stat_hp_base</t>
+          <t>stat_hp_per_level</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>플레이어 기본 체력</t>
+          <t>체력 강화 레벨당 증가</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stat_hp_per_level</t>
+          <t>stat_hp_max_level</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>체력 강화 레벨당 증가</t>
+          <t>체력 최대 강화 레벨</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stat_hp_max_level</t>
+          <t>stat_hp_cost</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>체력 최대 강화 레벨</t>
+          <t>체력 강화 기본 비용(실제=base*(레벨+1))</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stat_hp_cost</t>
+          <t>stat_speed_base</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>280</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>체력 강화 기본 비용(실제=base*(레벨+1))</t>
+          <t>플레이어 기본 이동속도(px/s)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stat_speed_base</t>
+          <t>stat_speed_per_level</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>플레이어 기본 이동속도(px/s)</t>
+          <t>이동속도 강화 레벨당 증가</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>stat_speed_per_level</t>
+          <t>stat_speed_max_level</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>이동속도 강화 레벨당 증가</t>
+          <t>이동속도 최대 강화 레벨</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stat_speed_max_level</t>
+          <t>stat_speed_cost</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>이동속도 최대 강화 레벨</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>stat_speed_cost</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>이동속도 강화 기본 비용(실제=base*(레벨+1))</t>
         </is>

--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -714,6 +714,21 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>carry_max_weight</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>플레이어가 가져갈 수 있는 최대 무게</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -477,22 +477,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>night_seconds</t>
+          <t>pistol_range</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>밤 쿠킹 세션 시간(초)</t>
+          <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>target_satisfaction</t>
+          <t>knife_range</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -500,230 +500,200 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>밤 성공에 필요한 만족 목표치</t>
+          <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pistol_range</t>
+          <t>camp_god_x</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>권총 사거리(px) — 총알이 날아가는 최대 거리</t>
+          <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>knife_range</t>
+          <t>camp_god_y</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>0.44</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>칼 근접 사거리(px) — 부채꼴 타격 반경</t>
+          <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>camp_god_x</t>
+          <t>camp_player_x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>캠프 god 가로 위치(바닥 비율 0~1)</t>
+          <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>camp_god_y</t>
+          <t>camp_player_y</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>캠프 god 세로 위치(바닥 비율 0~1)</t>
+          <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>camp_player_x</t>
+          <t>stat_hp_base</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.45</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>캠프 플레이어 가로 위치(바닥 비율 0~1)</t>
+          <t>플레이어 기본 체력</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>camp_player_y</t>
+          <t>stat_hp_per_level</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>캠프 플레이어 세로 위치(바닥 비율 0~1)</t>
+          <t>체력 강화 레벨당 증가</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stat_hp_base</t>
+          <t>stat_hp_max_level</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>플레이어 기본 체력</t>
+          <t>체력 최대 강화 레벨</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stat_hp_per_level</t>
+          <t>stat_hp_cost</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>체력 강화 레벨당 증가</t>
+          <t>체력 강화 기본 비용(실제=base*(레벨+1))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stat_hp_max_level</t>
+          <t>stat_speed_base</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>280</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>체력 최대 강화 레벨</t>
+          <t>플레이어 기본 이동속도(px/s)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stat_hp_cost</t>
+          <t>stat_speed_per_level</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>체력 강화 기본 비용(실제=base*(레벨+1))</t>
+          <t>이동속도 강화 레벨당 증가</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stat_speed_base</t>
+          <t>stat_speed_max_level</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>플레이어 기본 이동속도(px/s)</t>
+          <t>이동속도 최대 강화 레벨</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stat_speed_per_level</t>
+          <t>stat_speed_cost</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>이동속도 강화 레벨당 증가</t>
+          <t>이동속도 강화 기본 비용(실제=base*(레벨+1))</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>stat_speed_max_level</t>
+          <t>carry_max_weight</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>이동속도 최대 강화 레벨</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>stat_speed_cost</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>이동속도 강화 기본 비용(실제=base*(레벨+1))</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>carry_max_weight</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>50</v>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>플레이어가 가져갈 수 있는 최대 무게</t>
         </is>

--- a/data/balance.xlsx
+++ b/data/balance.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="day_targets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -31,13 +32,22 @@
       <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F6D7A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,8 +62,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -419,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -699,6 +712,159 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>camera_zoom</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>탐사 카메라 줌(정수 권장: 2 = 넓게 보기, 3 = 예전 화면 크기와 같은 비율)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>target_satisfaction</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>첫날 — 기본 레시피 A등급 2~3번이면 달성</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>레시피 강화가 필요해지기 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>125</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>160</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>180</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>200</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>이후 날은 마지막 값(200) 유지 — 더 늘리려면 행 추가</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
